--- a/public/templates/学生名单导入模板.xlsx
+++ b/public/templates/学生名单导入模板.xlsx
@@ -425,14 +425,14 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
